--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$107</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3836,8 +3836,74 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Hot Selling High Home Quality Steel Door Turkey Doors Security Entrance Exterior</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>140011500</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>https://m.made-in-china.com/product/Hot-Selling-High-Home-Quality-Steel-Door-Tur</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>wholesale steel door turkey exporter</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20 reactions · 27 shares - "Steel security doors with Anti-intrusion grill with </t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>0705656565</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>hello@eurodoor.co.ke</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/eurodoor.kenya/videos/steel-security-doors-with-anti-in</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>armored door supplier south africa kenya</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G105"/>
+  <autoFilter ref="A1:G107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$111</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3972,8 +3972,74 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>أبواب تركية</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>المغرب</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>905558781226</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adwhit.com/ar/أبواب-تركية-281753</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>مستورد ابواب تركية الدار البيضاء</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>ابواب حديديه خارجيه منزلقه سحاب</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>مصر</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>0595008118</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>ehostingstore@gmail.com</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>https://doors-store.com/ابواب-حديديه-خارجيه-منزلقه-سحاب/</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>تجار ابواب حديدية في مصر</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G109"/>
+  <autoFilter ref="A1:G111"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$122</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4364,8 +4364,43 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Steel Door Turkey Exporters Suppliers &amp; Manufacturers in Turkey</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>133910521, 200820130829</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>eg.sample@xyz.com</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>https://turkey.tradekey.com/steel-door-turkey.htm</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>wholesale steel door turkey exporter</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G121"/>
+  <autoFilter ref="A1:G122"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$130</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4636,8 +4636,43 @@
         </is>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>THE UK'S LEADING INSTALLER OF STEEL DOORS</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>الاردن</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>01785526016</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>sales@steeldoorcompany.co.uk</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>https://steeldoorcompany.co.uk/?srsltid=AfmBOoo9T-FwuOkCyhmHop632VW7CmUnDQujUUeo</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer jordan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G129"/>
+  <autoFilter ref="A1:G130"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$132</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G130"/>
+  <dimension ref="A1:G132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4671,8 +4671,74 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Wooden Doors in UAE</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>919700318318, 919953717914, 971551000655</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr"/>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.exportersindia.com/ae/wooden-doors.htm</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>site:exportersindia.com steel door africa</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 Chinese Steel Door Brands in 2026 - Best Steel Door Manufacturers in Chin</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>200810233332, 200920120943, 201220683975, 201230612642, 201320866401, 201320866708, 201330414830, 201330414858, 201330477623, 201330642561, 201420179526, 201430122726, 201430122747, 201430271750, 201510415666, 201530268284, 201610379518, 201621324852, 201630038274, 201630346580, 201630346583, 201630346590, 201630346591, 201630346592, 201630602263, 209092017, 249302010, 249362010, 377727587, 382972019, 395262020, 395832020, 8613557317112, 8618587696, 8618587696286</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>catherine@zonledoors.com</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zonledoors.com/top-10-chinese-steel-door-brands-in-2025-best-steel-d</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>best steel door manufacturer istanbul</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G130"/>
+  <autoFilter ref="A1:G132"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4768,8 +4768,39 @@
         </is>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>ابواب مصفحة في مصر</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>مصر</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>01031918915</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr"/>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dubizzle.com.eg/home-furniture-decor/q-ابواب-مصفحة/</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>مستورد ابواب مصفحة من تركيا القاهرة</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G133"/>
+  <autoFilter ref="A1:G134"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$137</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G136"/>
+  <dimension ref="A1:G137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4865,8 +4865,43 @@
         </is>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Iraq Steel Buyers Importers Distributors Wholesale agents and Resellers relat</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>العراق</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>201304304</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>eg.sample@xyz.com</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>https://importer.tradekey.com/iraq/steel.htm</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>steel door iraq importer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G136"/>
+  <autoFilter ref="A1:G137"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$140</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4931,8 +4931,74 @@
         </is>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>ابواب مصفحة ابواب داخلية</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>العراق</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>01110289808</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr"/>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>https://abwaboctober.blogspot.com/2016/08/5.html</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>موزع ابواب مصفحة في بغداد</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>ابواب مصفحة</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>العراق</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>010700700520127</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>aboalam122@icloud.com</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>https://aboalam-factory.com/ابواب-مصفحة/</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>موزع ابواب مصفحة في بغداد</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G138"/>
+  <autoFilter ref="A1:G140"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$148</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5222,8 +5222,39 @@
         </is>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Turkey Steel Door Manufacturers &amp; Suppliers</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>315011000</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr"/>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.made-in-china.com/manufacturers/turkey-steel-door.html</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>steel door factory turkey contact</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G147"/>
+  <autoFilter ref="A1:G148"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$149</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G148"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5253,8 +5253,39 @@
         </is>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>transfer surfaces suppliers</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>011021076080</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr"/>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.alibaba.com/transfer-surfaces-suppliers.html</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>site:alibaba.com steel security door turkey</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G148"/>
+  <autoFilter ref="A1:G149"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>